--- a/Thesis_result_figure/RAW_SA_experiment/24_6_1.6_200.xlsx
+++ b/Thesis_result_figure/RAW_SA_experiment/24_6_1.6_200.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1bs\lyhbs\dfjsp_ppo_\Thesis_result_figure\RAW_SA_experiment\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{882F86B4-254A-4C8E-8D9D-2BEA259F5596}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15796" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="win rate" sheetId="1" r:id="rId1"/>
@@ -13,7 +19,7 @@
     <sheet name="maximum" sheetId="4" r:id="rId4"/>
     <sheet name="before win rate" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="181029"/>
 </workbook>
 </file>
 
@@ -41,12 +47,12 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -54,17 +60,37 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="宋体"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <family val="2"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -91,27 +117,40 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyAlignment="1"/>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="2">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="好" xfId="1" builtinId="26"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -149,7 +188,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -183,6 +222,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -217,9 +257,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -392,11 +433,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -416,7 +457,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
@@ -437,16 +478,17 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:F52"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -466,7 +508,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>37587</v>
       </c>
@@ -486,7 +528,7 @@
         <v>36005</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>44415</v>
       </c>
@@ -506,7 +548,7 @@
         <v>28183</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>27439</v>
       </c>
@@ -526,7 +568,7 @@
         <v>33674</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>31136</v>
       </c>
@@ -546,7 +588,7 @@
         <v>31613</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>43445</v>
       </c>
@@ -566,7 +608,7 @@
         <v>34895</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>32085</v>
       </c>
@@ -586,7 +628,7 @@
         <v>28159</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>32630</v>
       </c>
@@ -606,7 +648,7 @@
         <v>29048</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>40438</v>
       </c>
@@ -626,7 +668,7 @@
         <v>31362</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>41411</v>
       </c>
@@ -646,7 +688,7 @@
         <v>32765</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>34784</v>
       </c>
@@ -666,7 +708,7 @@
         <v>30808</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>41732</v>
       </c>
@@ -686,7 +728,7 @@
         <v>25507</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>36386</v>
       </c>
@@ -706,7 +748,7 @@
         <v>28413</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>39203</v>
       </c>
@@ -726,7 +768,7 @@
         <v>30599</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>56607</v>
       </c>
@@ -746,7 +788,7 @@
         <v>33251</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>44418</v>
       </c>
@@ -766,7 +808,7 @@
         <v>38159</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>31733</v>
       </c>
@@ -786,7 +828,7 @@
         <v>34698</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>29676</v>
       </c>
@@ -806,7 +848,7 @@
         <v>34800</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>40336</v>
       </c>
@@ -826,7 +868,7 @@
         <v>36054</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>33527</v>
       </c>
@@ -846,7 +888,7 @@
         <v>24908</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>44324</v>
       </c>
@@ -866,7 +908,7 @@
         <v>35827</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>33152</v>
       </c>
@@ -886,7 +928,7 @@
         <v>37680</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>43361</v>
       </c>
@@ -906,7 +948,7 @@
         <v>30951</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>42360</v>
       </c>
@@ -926,7 +968,7 @@
         <v>37007</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>47634</v>
       </c>
@@ -946,7 +988,7 @@
         <v>36068</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>45097</v>
       </c>
@@ -966,7 +1008,7 @@
         <v>28219</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>29788</v>
       </c>
@@ -986,7 +1028,7 @@
         <v>29408</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>34737</v>
       </c>
@@ -1006,7 +1048,7 @@
         <v>23703</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>37404</v>
       </c>
@@ -1026,7 +1068,7 @@
         <v>32291</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>43915</v>
       </c>
@@ -1046,7 +1088,7 @@
         <v>39804</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>49919</v>
       </c>
@@ -1066,7 +1108,7 @@
         <v>33834</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>30783</v>
       </c>
@@ -1086,7 +1128,7 @@
         <v>29676</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>48059</v>
       </c>
@@ -1106,7 +1148,7 @@
         <v>35059</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>32621</v>
       </c>
@@ -1126,7 +1168,7 @@
         <v>37408</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>33419</v>
       </c>
@@ -1146,7 +1188,7 @@
         <v>26682</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>49879</v>
       </c>
@@ -1166,7 +1208,7 @@
         <v>31149</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>43189</v>
       </c>
@@ -1186,7 +1228,7 @@
         <v>34733</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>30784</v>
       </c>
@@ -1206,7 +1248,7 @@
         <v>25835</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>51490</v>
       </c>
@@ -1226,7 +1268,7 @@
         <v>35319</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>44010</v>
       </c>
@@ -1246,7 +1288,7 @@
         <v>30131</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>47518</v>
       </c>
@@ -1266,7 +1308,7 @@
         <v>36870</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>40084</v>
       </c>
@@ -1286,7 +1328,7 @@
         <v>33371</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>32145</v>
       </c>
@@ -1306,7 +1348,7 @@
         <v>28408</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>35963</v>
       </c>
@@ -1326,7 +1368,7 @@
         <v>32500</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>46730</v>
       </c>
@@ -1346,7 +1388,7 @@
         <v>36157</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>39270</v>
       </c>
@@ -1366,7 +1408,7 @@
         <v>33944</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>43426</v>
       </c>
@@ -1386,7 +1428,7 @@
         <v>39886</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>49387</v>
       </c>
@@ -1406,7 +1448,7 @@
         <v>33020</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>46794</v>
       </c>
@@ -1426,7 +1468,7 @@
         <v>35728</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>39858</v>
       </c>
@@ -1446,7 +1488,7 @@
         <v>26027</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>45824</v>
       </c>
@@ -1466,17 +1508,44 @@
         <v>38990</v>
       </c>
     </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="2">
+        <f>AVERAGE(A2:A51)</f>
+        <v>40038.239999999998</v>
+      </c>
+      <c r="B52" s="2">
+        <f t="shared" ref="B52:F52" si="0">AVERAGE(B2:B51)</f>
+        <v>35047.620000000003</v>
+      </c>
+      <c r="C52" s="2">
+        <f t="shared" si="0"/>
+        <v>34228.400000000001</v>
+      </c>
+      <c r="D52" s="2">
+        <f t="shared" si="0"/>
+        <v>32199.56</v>
+      </c>
+      <c r="E52" s="2">
+        <f t="shared" si="0"/>
+        <v>42346.58</v>
+      </c>
+      <c r="F52" s="2">
+        <f t="shared" si="0"/>
+        <v>32571.72</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1496,289 +1565,289 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0.8421052631578947</v>
+        <v>0.84210526315789469</v>
       </c>
       <c r="B2">
-        <v>0.7393364928909952</v>
+        <v>0.73933649289099523</v>
       </c>
       <c r="C2">
         <v>0.8779342723004695</v>
       </c>
       <c r="D2">
-        <v>0.9146919431279621</v>
+        <v>0.91469194312796209</v>
       </c>
       <c r="E2">
-        <v>0.8790697674418605</v>
+        <v>0.87906976744186049</v>
       </c>
       <c r="F2">
-        <v>0.8578199052132701</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
+        <v>0.85781990521327012</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>0.863849765258216</v>
       </c>
       <c r="B3">
-        <v>0.7677725118483413</v>
+        <v>0.76777251184834128</v>
       </c>
       <c r="C3">
-        <v>0.8341232227488151</v>
+        <v>0.83412322274881512</v>
       </c>
       <c r="D3">
-        <v>0.8967136150234741</v>
+        <v>0.89671361502347413</v>
       </c>
       <c r="E3">
-        <v>0.8104265402843602</v>
+        <v>0.81042654028436023</v>
       </c>
       <c r="F3">
-        <v>0.8325581395348837</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
+        <v>0.83255813953488367</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>0.7699530516431925</v>
       </c>
       <c r="B4">
-        <v>0.8075117370892019</v>
+        <v>0.80751173708920188</v>
       </c>
       <c r="C4">
-        <v>0.8909952606635071</v>
+        <v>0.89099526066350709</v>
       </c>
       <c r="D4">
-        <v>0.8909952606635071</v>
+        <v>0.89099526066350709</v>
       </c>
       <c r="E4">
-        <v>0.8169014084507042</v>
+        <v>0.81690140845070425</v>
       </c>
       <c r="F4">
-        <v>0.8625592417061612</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>0.86255924170616116</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0.7934272300469484</v>
+        <v>0.79342723004694837</v>
       </c>
       <c r="B5">
-        <v>0.7887323943661971</v>
+        <v>0.78873239436619713</v>
       </c>
       <c r="C5">
-        <v>0.8388625592417062</v>
+        <v>0.83886255924170616</v>
       </c>
       <c r="D5">
-        <v>0.9162790697674419</v>
+        <v>0.91627906976744189</v>
       </c>
       <c r="E5">
-        <v>0.8672985781990521</v>
+        <v>0.86729857819905209</v>
       </c>
       <c r="F5">
-        <v>0.813953488372093</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>0.81395348837209303</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.8790697674418605</v>
+        <v>0.87906976744186049</v>
       </c>
       <c r="B6">
-        <v>0.7298578199052133</v>
+        <v>0.72985781990521326</v>
       </c>
       <c r="C6">
-        <v>0.813953488372093</v>
+        <v>0.81395348837209303</v>
       </c>
       <c r="D6">
-        <v>0.8530805687203792</v>
+        <v>0.85308056872037918</v>
       </c>
       <c r="E6">
         <v>0.8564593301435407</v>
       </c>
       <c r="F6">
-        <v>0.8790697674418605</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>0.87906976744186049</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0.8009478672985783</v>
+        <v>0.80094786729857825</v>
       </c>
       <c r="B7">
-        <v>0.7894736842105263</v>
+        <v>0.78947368421052633</v>
       </c>
       <c r="C7">
-        <v>0.7777777777777778</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="D7">
-        <v>0.8685446009389671</v>
+        <v>0.86854460093896713</v>
       </c>
       <c r="E7">
-        <v>0.9107981220657277</v>
+        <v>0.91079812206572774</v>
       </c>
       <c r="F7">
-        <v>0.8372093023255814</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>0.83720930232558144</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>0.8293838862559242</v>
+        <v>0.82938388625592419</v>
       </c>
       <c r="B8">
-        <v>0.8181818181818182</v>
+        <v>0.81818181818181823</v>
       </c>
       <c r="C8">
-        <v>0.8075117370892019</v>
+        <v>0.80751173708920188</v>
       </c>
       <c r="D8">
-        <v>0.8967136150234741</v>
+        <v>0.89671361502347413</v>
       </c>
       <c r="E8">
-        <v>0.8246445497630331</v>
+        <v>0.82464454976303314</v>
       </c>
       <c r="F8">
-        <v>0.8578199052132701</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>0.85781990521327012</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>0.8558139534883721</v>
+        <v>0.85581395348837208</v>
       </c>
       <c r="B9">
-        <v>0.7581395348837209</v>
+        <v>0.75813953488372088</v>
       </c>
       <c r="C9">
-        <v>0.8604651162790697</v>
+        <v>0.86046511627906974</v>
       </c>
       <c r="D9">
-        <v>0.9082125603864735</v>
+        <v>0.90821256038647347</v>
       </c>
       <c r="E9">
-        <v>0.8262910798122066</v>
+        <v>0.82629107981220662</v>
       </c>
       <c r="F9">
-        <v>0.8215962441314554</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>0.82159624413145538</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>0.8497652582159625</v>
+        <v>0.84976525821596249</v>
       </c>
       <c r="B10">
-        <v>0.7605633802816901</v>
+        <v>0.76056338028169013</v>
       </c>
       <c r="C10">
-        <v>0.8246445497630331</v>
+        <v>0.82464454976303314</v>
       </c>
       <c r="D10">
-        <v>0.8483412322274881</v>
+        <v>0.84834123222748814</v>
       </c>
       <c r="E10">
-        <v>0.861244019138756</v>
+        <v>0.86124401913875603</v>
       </c>
       <c r="F10">
-        <v>0.8215962441314554</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>0.82159624413145538</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>0.863849765258216</v>
       </c>
       <c r="B11">
-        <v>0.7129186602870813</v>
+        <v>0.71291866028708128</v>
       </c>
       <c r="C11">
-        <v>0.8246445497630331</v>
+        <v>0.82464454976303314</v>
       </c>
       <c r="D11">
-        <v>0.9209302325581395</v>
+        <v>0.92093023255813955</v>
       </c>
       <c r="E11">
-        <v>0.8325358851674641</v>
+        <v>0.83253588516746413</v>
       </c>
       <c r="F11">
-        <v>0.8862559241706162</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>0.88625592417061616</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>0.8976744186046511</v>
+        <v>0.89767441860465114</v>
       </c>
       <c r="B12">
-        <v>0.8450704225352113</v>
+        <v>0.84507042253521125</v>
       </c>
       <c r="C12">
-        <v>0.8293838862559242</v>
+        <v>0.82938388625592419</v>
       </c>
       <c r="D12">
-        <v>0.9146919431279621</v>
+        <v>0.91469194312796209</v>
       </c>
       <c r="E12">
-        <v>0.8873239436619719</v>
+        <v>0.88732394366197187</v>
       </c>
       <c r="F12">
-        <v>0.8497652582159625</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>0.84976525821596249</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
-        <v>0.8465116279069768</v>
+        <v>0.84651162790697676</v>
       </c>
       <c r="B13">
-        <v>0.8028169014084507</v>
+        <v>0.80281690140845074</v>
       </c>
       <c r="C13">
         <v>0.9023255813953488</v>
       </c>
       <c r="D13">
-        <v>0.9043062200956937</v>
+        <v>0.90430622009569372</v>
       </c>
       <c r="E13">
-        <v>0.8199052132701422</v>
+        <v>0.81990521327014221</v>
       </c>
       <c r="F13">
-        <v>0.8436018957345972</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+        <v>0.84360189573459721</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
-        <v>0.8883720930232558</v>
+        <v>0.88837209302325582</v>
       </c>
       <c r="B14">
-        <v>0.8169014084507042</v>
+        <v>0.81690140845070425</v>
       </c>
       <c r="C14">
-        <v>0.8883720930232558</v>
+        <v>0.88837209302325582</v>
       </c>
       <c r="D14">
-        <v>0.9052132701421801</v>
+        <v>0.90521327014218012</v>
       </c>
       <c r="E14">
-        <v>0.8578199052132701</v>
+        <v>0.85781990521327012</v>
       </c>
       <c r="F14">
-        <v>0.827906976744186</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
+        <v>0.82790697674418601</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
-        <v>0.8976744186046511</v>
+        <v>0.89767441860465114</v>
       </c>
       <c r="B15">
-        <v>0.8403755868544601</v>
+        <v>0.84037558685446012</v>
       </c>
       <c r="C15">
-        <v>0.8720379146919431</v>
+        <v>0.87203791469194314</v>
       </c>
       <c r="D15">
-        <v>0.8341232227488151</v>
+        <v>0.83412322274881512</v>
       </c>
       <c r="E15">
-        <v>0.8356807511737089</v>
+        <v>0.83568075117370888</v>
       </c>
       <c r="F15">
-        <v>0.8720379146919431</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
+        <v>0.87203791469194314</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
-        <v>0.8744186046511628</v>
+        <v>0.87441860465116283</v>
       </c>
       <c r="B16">
         <v>0.7109004739336493</v>
@@ -1787,238 +1856,238 @@
         <v>0.863849765258216</v>
       </c>
       <c r="D16">
-        <v>0.9052132701421801</v>
+        <v>0.90521327014218012</v>
       </c>
       <c r="E16">
-        <v>0.8293838862559242</v>
+        <v>0.82938388625592419</v>
       </c>
       <c r="F16">
-        <v>0.813953488372093</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
+        <v>0.81395348837209303</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
-        <v>0.8544600938967136</v>
+        <v>0.85446009389671362</v>
       </c>
       <c r="B17">
-        <v>0.7746478873239436</v>
+        <v>0.77464788732394363</v>
       </c>
       <c r="C17">
         <v>0.9138755980861244</v>
       </c>
       <c r="D17">
-        <v>0.8356807511737089</v>
+        <v>0.83568075117370888</v>
       </c>
       <c r="E17">
-        <v>0.7934272300469484</v>
+        <v>0.79342723004694837</v>
       </c>
       <c r="F17">
-        <v>0.8260869565217391</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
+        <v>0.82608695652173914</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>0.7746478873239436</v>
+        <v>0.77464788732394363</v>
       </c>
       <c r="B18">
-        <v>0.7302325581395349</v>
+        <v>0.73023255813953492</v>
       </c>
       <c r="C18">
         <v>0.8651162790697674</v>
       </c>
       <c r="D18">
-        <v>0.8873239436619719</v>
+        <v>0.88732394366197187</v>
       </c>
       <c r="E18">
-        <v>0.812206572769953</v>
+        <v>0.81220657276995301</v>
       </c>
       <c r="F18">
-        <v>0.9116279069767442</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
+        <v>0.91162790697674423</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
-        <v>0.8591549295774648</v>
+        <v>0.85915492957746475</v>
       </c>
       <c r="B19">
-        <v>0.7674418604651163</v>
+        <v>0.76744186046511631</v>
       </c>
       <c r="C19">
         <v>0.8046511627906977</v>
       </c>
       <c r="D19">
-        <v>0.933649289099526</v>
+        <v>0.93364928909952605</v>
       </c>
       <c r="E19">
-        <v>0.8151658767772512</v>
+        <v>0.81516587677725116</v>
       </c>
       <c r="F19">
-        <v>0.8720379146919431</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
+        <v>0.87203791469194314</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
-        <v>0.8405797101449275</v>
+        <v>0.84057971014492749</v>
       </c>
       <c r="B20">
         <v>0.7981220657276995</v>
       </c>
       <c r="C20">
-        <v>0.8697674418604651</v>
+        <v>0.86976744186046506</v>
       </c>
       <c r="D20">
         <v>0.9138755980861244</v>
       </c>
       <c r="E20">
-        <v>0.8465116279069768</v>
+        <v>0.84651162790697676</v>
       </c>
       <c r="F20">
-        <v>0.8530805687203792</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
+        <v>0.85308056872037918</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
-        <v>0.9395348837209302</v>
+        <v>0.93953488372093019</v>
       </c>
       <c r="B21">
-        <v>0.7511737089201878</v>
+        <v>0.75117370892018775</v>
       </c>
       <c r="C21">
         <v>0.8564593301435407</v>
       </c>
       <c r="D21">
-        <v>0.8862559241706162</v>
+        <v>0.88625592417061616</v>
       </c>
       <c r="E21">
-        <v>0.8009478672985783</v>
+        <v>0.80094786729857825</v>
       </c>
       <c r="F21">
-        <v>0.8803827751196173</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
+        <v>0.88038277511961727</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
-        <v>0.7906976744186046</v>
+        <v>0.79069767441860461</v>
       </c>
       <c r="B22">
-        <v>0.7534883720930232</v>
+        <v>0.75348837209302322</v>
       </c>
       <c r="C22">
-        <v>0.8544600938967136</v>
+        <v>0.85446009389671362</v>
       </c>
       <c r="D22">
         <v>0.8564593301435407</v>
       </c>
       <c r="E22">
-        <v>0.8325581395348837</v>
+        <v>0.83255813953488367</v>
       </c>
       <c r="F22">
-        <v>0.8744186046511628</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
+        <v>0.87441860465116283</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
-        <v>0.8591549295774648</v>
+        <v>0.85915492957746475</v>
       </c>
       <c r="B23">
-        <v>0.7767441860465116</v>
+        <v>0.77674418604651163</v>
       </c>
       <c r="C23">
-        <v>0.8695652173913043</v>
+        <v>0.86956521739130432</v>
       </c>
       <c r="D23">
-        <v>0.8967136150234741</v>
+        <v>0.89671361502347413</v>
       </c>
       <c r="E23">
-        <v>0.8357487922705314</v>
+        <v>0.83574879227053145</v>
       </c>
       <c r="F23">
-        <v>0.8356807511737089</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
+        <v>0.83568075117370888</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
-        <v>0.8899521531100478</v>
+        <v>0.88995215311004783</v>
       </c>
       <c r="B24">
-        <v>0.7630331753554502</v>
+        <v>0.76303317535545023</v>
       </c>
       <c r="C24">
-        <v>0.8388625592417062</v>
+        <v>0.83886255924170616</v>
       </c>
       <c r="D24">
-        <v>0.8967136150234741</v>
+        <v>0.89671361502347413</v>
       </c>
       <c r="E24">
-        <v>0.8516746411483254</v>
+        <v>0.85167464114832536</v>
       </c>
       <c r="F24">
         <v>0.9023255813953488</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
-        <v>0.8697674418604651</v>
+        <v>0.86976744186046506</v>
       </c>
       <c r="B25">
-        <v>0.8277511961722488</v>
+        <v>0.82775119617224879</v>
       </c>
       <c r="C25">
-        <v>0.7674418604651163</v>
+        <v>0.76744186046511631</v>
       </c>
       <c r="D25">
-        <v>0.8720379146919431</v>
+        <v>0.87203791469194314</v>
       </c>
       <c r="E25">
         <v>0.8046511627906977</v>
       </c>
       <c r="F25">
-        <v>0.8815165876777251</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>0.88151658767772512</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>0.8564593301435407</v>
       </c>
       <c r="B26">
-        <v>0.6966824644549763</v>
+        <v>0.69668246445497628</v>
       </c>
       <c r="C26">
-        <v>0.8862559241706162</v>
+        <v>0.88625592417061616</v>
       </c>
       <c r="D26">
-        <v>0.9107981220657277</v>
+        <v>0.91079812206572774</v>
       </c>
       <c r="E26">
-        <v>0.8862559241706162</v>
+        <v>0.88625592417061616</v>
       </c>
       <c r="F26">
-        <v>0.8767772511848341</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>0.87677725118483407</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
-        <v>0.8075117370892019</v>
+        <v>0.80751173708920188</v>
       </c>
       <c r="B27">
-        <v>0.7464788732394366</v>
+        <v>0.74647887323943662</v>
       </c>
       <c r="C27">
-        <v>0.8502415458937198</v>
+        <v>0.85024154589371981</v>
       </c>
       <c r="D27">
-        <v>0.8851674641148325</v>
+        <v>0.88516746411483249</v>
       </c>
       <c r="E27">
-        <v>0.8544600938967136</v>
+        <v>0.85446009389671362</v>
       </c>
       <c r="F27">
-        <v>0.8309859154929577</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>0.83098591549295775</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
-        <v>0.8516746411483254</v>
+        <v>0.85167464114832536</v>
       </c>
       <c r="B28">
         <v>0.7345971563981043</v>
@@ -2027,44 +2096,44 @@
         <v>0.8564593301435407</v>
       </c>
       <c r="D28">
-        <v>0.9154929577464789</v>
+        <v>0.91549295774647887</v>
       </c>
       <c r="E28">
-        <v>0.8186046511627907</v>
+        <v>0.81860465116279069</v>
       </c>
       <c r="F28">
-        <v>0.8056872037914692</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>0.80568720379146919</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
-        <v>0.8862559241706162</v>
+        <v>0.88625592417061616</v>
       </c>
       <c r="B29">
         <v>0.6398104265402843</v>
       </c>
       <c r="C29">
-        <v>0.8341232227488151</v>
+        <v>0.83412322274881512</v>
       </c>
       <c r="D29">
-        <v>0.943127962085308</v>
+        <v>0.94312796208530802</v>
       </c>
       <c r="E29">
-        <v>0.8708133971291866</v>
+        <v>0.87081339712918659</v>
       </c>
       <c r="F29">
         <v>0.8418604651162791</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
-        <v>0.8558139534883721</v>
+        <v>0.85581395348837208</v>
       </c>
       <c r="B30">
-        <v>0.7819905213270142</v>
+        <v>0.78199052132701419</v>
       </c>
       <c r="C30">
-        <v>0.9069767441860465</v>
+        <v>0.90697674418604646</v>
       </c>
       <c r="D30">
         <v>0.9061032863849765</v>
@@ -2073,330 +2142,330 @@
         <v>0.784037558685446</v>
       </c>
       <c r="F30">
-        <v>0.8511627906976744</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>0.85116279069767442</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
-        <v>0.9162790697674419</v>
+        <v>0.91627906976744189</v>
       </c>
       <c r="B31">
-        <v>0.7772511848341233</v>
+        <v>0.77725118483412325</v>
       </c>
       <c r="C31">
-        <v>0.8708133971291866</v>
+        <v>0.87081339712918659</v>
       </c>
       <c r="D31">
-        <v>0.8957345971563981</v>
+        <v>0.89573459715639814</v>
       </c>
       <c r="E31">
-        <v>0.7914691943127962</v>
+        <v>0.79146919431279616</v>
       </c>
       <c r="F31">
         <v>0.9061032863849765</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
-        <v>0.8169014084507042</v>
+        <v>0.81690140845070425</v>
       </c>
       <c r="B32">
-        <v>0.8186046511627907</v>
+        <v>0.81860465116279069</v>
       </c>
       <c r="C32">
-        <v>0.8591549295774648</v>
+        <v>0.85915492957746475</v>
       </c>
       <c r="D32">
-        <v>0.9154929577464789</v>
+        <v>0.91549295774647887</v>
       </c>
       <c r="E32">
-        <v>0.8436018957345972</v>
+        <v>0.84360189573459721</v>
       </c>
       <c r="F32">
-        <v>0.8465116279069768</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>0.84651162790697676</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
-        <v>0.9162790697674419</v>
+        <v>0.91627906976744189</v>
       </c>
       <c r="B33">
-        <v>0.8009478672985783</v>
+        <v>0.80094786729857825</v>
       </c>
       <c r="C33">
-        <v>0.8405797101449275</v>
+        <v>0.84057971014492749</v>
       </c>
       <c r="D33">
-        <v>0.8957345971563981</v>
+        <v>0.89573459715639814</v>
       </c>
       <c r="E33">
-        <v>0.8293838862559242</v>
+        <v>0.82938388625592419</v>
       </c>
       <c r="F33">
-        <v>0.8591549295774648</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>0.85915492957746475</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
-        <v>0.8199052132701422</v>
+        <v>0.81990521327014221</v>
       </c>
       <c r="B34">
-        <v>0.8056872037914692</v>
+        <v>0.80568720379146919</v>
       </c>
       <c r="C34">
-        <v>0.8862559241706162</v>
+        <v>0.88625592417061616</v>
       </c>
       <c r="D34">
-        <v>0.8403755868544601</v>
+        <v>0.84037558685446012</v>
       </c>
       <c r="E34">
-        <v>0.8093023255813954</v>
+        <v>0.80930232558139537</v>
       </c>
       <c r="F34">
-        <v>0.8883720930232558</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>0.88837209302325582</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
-        <v>0.8862559241706162</v>
+        <v>0.88625592417061616</v>
       </c>
       <c r="B35">
-        <v>0.8341232227488151</v>
+        <v>0.83412322274881512</v>
       </c>
       <c r="C35">
-        <v>0.9014084507042254</v>
+        <v>0.90140845070422537</v>
       </c>
       <c r="D35">
-        <v>0.8873239436619719</v>
+        <v>0.88732394366197187</v>
       </c>
       <c r="E35">
-        <v>0.7962085308056872</v>
+        <v>0.79620853080568721</v>
       </c>
       <c r="F35">
-        <v>0.8293838862559242</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>0.82938388625592419</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
-        <v>0.9014084507042254</v>
+        <v>0.90140845070422537</v>
       </c>
       <c r="B36">
-        <v>0.7867298578199052</v>
+        <v>0.78672985781990523</v>
       </c>
       <c r="C36">
-        <v>0.8516746411483254</v>
+        <v>0.85167464114832536</v>
       </c>
       <c r="D36">
-        <v>0.8755980861244019</v>
+        <v>0.87559808612440193</v>
       </c>
       <c r="E36">
-        <v>0.7942583732057417</v>
+        <v>0.79425837320574166</v>
       </c>
       <c r="F36">
-        <v>0.8967136150234741</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>0.89671361502347413</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
-        <v>0.8604651162790697</v>
+        <v>0.86046511627906974</v>
       </c>
       <c r="B37">
-        <v>0.7767441860465116</v>
+        <v>0.77674418604651163</v>
       </c>
       <c r="C37">
-        <v>0.8483412322274881</v>
+        <v>0.84834123222748814</v>
       </c>
       <c r="D37">
-        <v>0.8732394366197183</v>
+        <v>0.87323943661971826</v>
       </c>
       <c r="E37">
-        <v>0.8625592417061612</v>
+        <v>0.86255924170616116</v>
       </c>
       <c r="F37">
-        <v>0.8388625592417062</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>0.83886255924170616</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
-        <v>0.813953488372093</v>
+        <v>0.81395348837209303</v>
       </c>
       <c r="B38">
-        <v>0.7703349282296651</v>
+        <v>0.77033492822966509</v>
       </c>
       <c r="C38">
-        <v>0.8790697674418605</v>
+        <v>0.87906976744186049</v>
       </c>
       <c r="D38">
-        <v>0.9069767441860465</v>
+        <v>0.90697674418604646</v>
       </c>
       <c r="E38">
         <v>0.8564593301435407</v>
       </c>
       <c r="F38">
-        <v>0.8497652582159625</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>0.84976525821596249</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
-        <v>0.9043062200956937</v>
+        <v>0.90430622009569372</v>
       </c>
       <c r="B39">
-        <v>0.8215962441314554</v>
+        <v>0.82159624413145538</v>
       </c>
       <c r="C39">
-        <v>0.8403755868544601</v>
+        <v>0.84037558685446012</v>
       </c>
       <c r="D39">
-        <v>0.9043062200956937</v>
+        <v>0.90430622009569372</v>
       </c>
       <c r="E39">
-        <v>0.8578199052132701</v>
+        <v>0.85781990521327012</v>
       </c>
       <c r="F39">
-        <v>0.8075117370892019</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>0.80751173708920188</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
-        <v>0.8873239436619719</v>
+        <v>0.88732394366197187</v>
       </c>
       <c r="B40">
-        <v>0.7652582159624414</v>
+        <v>0.76525821596244137</v>
       </c>
       <c r="C40">
-        <v>0.8497652582159625</v>
+        <v>0.84976525821596249</v>
       </c>
       <c r="D40">
         <v>0.9061032863849765</v>
       </c>
       <c r="E40">
-        <v>0.8436018957345972</v>
+        <v>0.84360189573459721</v>
       </c>
       <c r="F40">
-        <v>0.8873239436619719</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>0.88732394366197187</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
-        <v>0.9130434782608695</v>
+        <v>0.91304347826086951</v>
       </c>
       <c r="B41">
-        <v>0.7894736842105263</v>
+        <v>0.78947368421052633</v>
       </c>
       <c r="C41">
-        <v>0.8767772511848341</v>
+        <v>0.87677725118483407</v>
       </c>
       <c r="D41">
-        <v>0.786046511627907</v>
+        <v>0.78604651162790695</v>
       </c>
       <c r="E41">
-        <v>0.812206572769953</v>
+        <v>0.81220657276995301</v>
       </c>
       <c r="F41">
-        <v>0.8815165876777251</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>0.88151658767772512</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
-        <v>0.8309859154929577</v>
+        <v>0.83098591549295775</v>
       </c>
       <c r="B42">
-        <v>0.7581395348837209</v>
+        <v>0.75813953488372088</v>
       </c>
       <c r="C42">
-        <v>0.9241706161137441</v>
+        <v>0.92417061611374407</v>
       </c>
       <c r="D42">
-        <v>0.9116279069767442</v>
+        <v>0.91162790697674423</v>
       </c>
       <c r="E42">
-        <v>0.8450704225352113</v>
+        <v>0.84507042253521125</v>
       </c>
       <c r="F42">
-        <v>0.8604651162790697</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>0.86046511627906974</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>0.8564593301435407</v>
       </c>
       <c r="B43">
-        <v>0.7894736842105263</v>
+        <v>0.78947368421052633</v>
       </c>
       <c r="C43">
         <v>0.8564593301435407</v>
       </c>
       <c r="D43">
-        <v>0.9248826291079812</v>
+        <v>0.92488262910798125</v>
       </c>
       <c r="E43">
-        <v>0.812206572769953</v>
+        <v>0.81220657276995301</v>
       </c>
       <c r="F43">
-        <v>0.8732394366197183</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>0.87323943661971826</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
-        <v>0.8325358851674641</v>
+        <v>0.83253588516746413</v>
       </c>
       <c r="B44">
-        <v>0.8075117370892019</v>
+        <v>0.80751173708920188</v>
       </c>
       <c r="C44">
-        <v>0.8436018957345972</v>
+        <v>0.84360189573459721</v>
       </c>
       <c r="D44">
-        <v>0.8720379146919431</v>
+        <v>0.87203791469194314</v>
       </c>
       <c r="E44">
-        <v>0.7582938388625592</v>
+        <v>0.75829383886255919</v>
       </c>
       <c r="F44">
-        <v>0.8967136150234741</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
+        <v>0.89671361502347413</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
-        <v>0.9004739336492891</v>
+        <v>0.90047393364928907</v>
       </c>
       <c r="B45">
-        <v>0.7703349282296651</v>
+        <v>0.77033492822966509</v>
       </c>
       <c r="C45">
-        <v>0.8516746411483254</v>
+        <v>0.85167464114832536</v>
       </c>
       <c r="D45">
-        <v>0.8957345971563981</v>
+        <v>0.89573459715639814</v>
       </c>
       <c r="E45">
-        <v>0.8708133971291866</v>
+        <v>0.87081339712918659</v>
       </c>
       <c r="F45">
-        <v>0.8625592417061612</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6">
+        <v>0.86255924170616116</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
-        <v>0.8685446009389671</v>
+        <v>0.86854460093896713</v>
       </c>
       <c r="B46">
-        <v>0.8186046511627907</v>
+        <v>0.81860465116279069</v>
       </c>
       <c r="C46">
-        <v>0.8803827751196173</v>
+        <v>0.88038277511961727</v>
       </c>
       <c r="D46">
-        <v>0.8325581395348837</v>
+        <v>0.83255813953488367</v>
       </c>
       <c r="E46">
-        <v>0.8388625592417062</v>
+        <v>0.83886255924170616</v>
       </c>
       <c r="F46">
-        <v>0.8660287081339713</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6">
+        <v>0.86602870813397126</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>0.8418604651162791</v>
       </c>
@@ -2404,109 +2473,110 @@
         <v>0.8046511627906977</v>
       </c>
       <c r="C47">
-        <v>0.9248826291079812</v>
+        <v>0.92488262910798125</v>
       </c>
       <c r="D47">
         <v>0.8779342723004695</v>
       </c>
       <c r="E47">
-        <v>0.8388625592417062</v>
+        <v>0.83886255924170616</v>
       </c>
       <c r="F47">
-        <v>0.9004739336492891</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6">
+        <v>0.90047393364928907</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
-        <v>0.8720379146919431</v>
+        <v>0.87203791469194314</v>
       </c>
       <c r="B48">
-        <v>0.7793427230046949</v>
+        <v>0.77934272300469487</v>
       </c>
       <c r="C48">
-        <v>0.8578199052132701</v>
+        <v>0.85781990521327012</v>
       </c>
       <c r="D48">
-        <v>0.9436619718309859</v>
+        <v>0.94366197183098588</v>
       </c>
       <c r="E48">
-        <v>0.8009478672985783</v>
+        <v>0.80094786729857825</v>
       </c>
       <c r="F48">
-        <v>0.9090909090909091</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6">
+        <v>0.90909090909090906</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
-        <v>0.8851674641148325</v>
+        <v>0.88516746411483249</v>
       </c>
       <c r="B49">
-        <v>0.7276995305164319</v>
+        <v>0.72769953051643188</v>
       </c>
       <c r="C49">
-        <v>0.8732394366197183</v>
+        <v>0.87323943661971826</v>
       </c>
       <c r="D49">
-        <v>0.9330143540669856</v>
+        <v>0.93301435406698563</v>
       </c>
       <c r="E49">
-        <v>0.8625592417061612</v>
+        <v>0.86255924170616116</v>
       </c>
       <c r="F49">
-        <v>0.9116279069767442</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6">
+        <v>0.91162790697674423</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>0.8564593301435407</v>
       </c>
       <c r="B50">
-        <v>0.722488038277512</v>
+        <v>0.72248803827751196</v>
       </c>
       <c r="C50">
-        <v>0.8873239436619719</v>
+        <v>0.88732394366197187</v>
       </c>
       <c r="D50">
-        <v>0.9014084507042254</v>
+        <v>0.90140845070422537</v>
       </c>
       <c r="E50">
         <v>0.8651162790697674</v>
       </c>
       <c r="F50">
-        <v>0.827906976744186</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6">
+        <v>0.82790697674418601</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
-        <v>0.8957345971563981</v>
+        <v>0.89573459715639814</v>
       </c>
       <c r="B51">
-        <v>0.7813953488372093</v>
+        <v>0.78139534883720929</v>
       </c>
       <c r="C51">
-        <v>0.8356807511737089</v>
+        <v>0.83568075117370888</v>
       </c>
       <c r="D51">
-        <v>0.9209302325581395</v>
+        <v>0.92093023255813955</v>
       </c>
       <c r="E51">
-        <v>0.84688995215311</v>
+        <v>0.84688995215311003</v>
       </c>
       <c r="F51">
-        <v>0.8558139534883721</v>
+        <v>0.85581395348837208</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:F51"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2526,7 +2596,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>433</v>
       </c>
@@ -2546,7 +2616,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>606</v>
       </c>
@@ -2566,7 +2636,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>453</v>
       </c>
@@ -2586,7 +2656,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>515</v>
       </c>
@@ -2606,7 +2676,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>575</v>
       </c>
@@ -2626,7 +2696,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>450</v>
       </c>
@@ -2646,7 +2716,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>472</v>
       </c>
@@ -2666,7 +2736,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>576</v>
       </c>
@@ -2686,7 +2756,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>536</v>
       </c>
@@ -2706,7 +2776,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>441</v>
       </c>
@@ -2726,7 +2796,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>512</v>
       </c>
@@ -2746,7 +2816,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>485</v>
       </c>
@@ -2766,7 +2836,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>505</v>
       </c>
@@ -2786,7 +2856,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>660</v>
       </c>
@@ -2806,7 +2876,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>537</v>
       </c>
@@ -2826,7 +2896,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>489</v>
       </c>
@@ -2846,7 +2916,7 @@
         <v>765</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>480</v>
       </c>
@@ -2866,7 +2936,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>549</v>
       </c>
@@ -2886,7 +2956,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>465</v>
       </c>
@@ -2906,7 +2976,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>521</v>
       </c>
@@ -2926,7 +2996,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="22" spans="1:6">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>475</v>
       </c>
@@ -2946,7 +3016,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>586</v>
       </c>
@@ -2966,7 +3036,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>523</v>
       </c>
@@ -2986,7 +3056,7 @@
         <v>522</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>649</v>
       </c>
@@ -3006,7 +3076,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>609</v>
       </c>
@@ -3026,7 +3096,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>503</v>
       </c>
@@ -3046,7 +3116,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="28" spans="1:6">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>457</v>
       </c>
@@ -3066,7 +3136,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="29" spans="1:6">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>548</v>
       </c>
@@ -3086,7 +3156,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="30" spans="1:6">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>558</v>
       </c>
@@ -3106,7 +3176,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="31" spans="1:6">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>550</v>
       </c>
@@ -3126,7 +3196,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="32" spans="1:6">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>417</v>
       </c>
@@ -3146,7 +3216,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="33" spans="1:6">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>626</v>
       </c>
@@ -3166,7 +3236,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="34" spans="1:6">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>559</v>
       </c>
@@ -3186,7 +3256,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="35" spans="1:6">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>460</v>
       </c>
@@ -3206,7 +3276,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="36" spans="1:6">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>612</v>
       </c>
@@ -3226,7 +3296,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="37" spans="1:6">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>555</v>
       </c>
@@ -3246,7 +3316,7 @@
         <v>571</v>
       </c>
     </row>
-    <row r="38" spans="1:6">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>461</v>
       </c>
@@ -3266,7 +3336,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="39" spans="1:6">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>559</v>
       </c>
@@ -3286,7 +3356,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="40" spans="1:6">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>576</v>
       </c>
@@ -3306,7 +3376,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="41" spans="1:6">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>644</v>
       </c>
@@ -3326,7 +3396,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="42" spans="1:6">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>534</v>
       </c>
@@ -3346,7 +3416,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="43" spans="1:6">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>462</v>
       </c>
@@ -3366,7 +3436,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="44" spans="1:6">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>447</v>
       </c>
@@ -3386,7 +3456,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="45" spans="1:6">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>579</v>
       </c>
@@ -3406,7 +3476,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="46" spans="1:6">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>516</v>
       </c>
@@ -3426,7 +3496,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="47" spans="1:6">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>488</v>
       </c>
@@ -3446,7 +3516,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="48" spans="1:6">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>591</v>
       </c>
@@ -3466,7 +3536,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="49" spans="1:6">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>555</v>
       </c>
@@ -3486,7 +3556,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="50" spans="1:6">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>488</v>
       </c>
@@ -3506,7 +3576,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="51" spans="1:6">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>550</v>
       </c>
@@ -3527,16 +3597,17 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:F2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3556,7 +3627,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>10</v>
       </c>
@@ -3577,6 +3648,7 @@
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>